--- a/docs/worklog.xlsx
+++ b/docs/worklog.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F69"/>
+  <dimension ref="A1:F344"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2647,6 +2647,8806 @@
         </is>
       </c>
     </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>12:27</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>Fix empty Day dropdown in Employee Shift Schedule form</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>964b3fdc</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>Fix 500 cancelling a permanent shift request (requested_till is None)</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>8aa8fd57</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>10:41</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>Fix remaining UTC-&gt;IST timezone bugs across attendance</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>78879b00</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>Fix mobile check-in/out storing UTC instead of IST times</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>b2894323</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>02:27</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>Apply same hardening to work-type request flow</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>f487d6f2</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>02:20</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>Tell approver why a shift request didn't apply + guard reallocate work info</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>336cf6da</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>02:15</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>Guard shift apply against missing work info + notify HR of shift requests</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>0b23e82c</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>02:05</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>Fix approved shift requests never applying to employee work info</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>0e88186e</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>01:58</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>Auto-enroll face baseline on first mobile check-in/out</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2f41c765</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>01:40</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>Grant geofencing + facedetection perms to company admin/HR roles</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>21e8b003</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>01:30</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>Fix shift-request approve 500 + shift-schedule silent no-op + API gate guard</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>22c33270</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>01:14</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>Fix 'Get My Current Location' button not working in geofence config</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>64eb5a1c</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>01:03</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>Shift-schedule dup check must bypass company scope (.entire)</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>13d1f7f7</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>01:00</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>Restrict policy acceptance status to HR/admin + scope to own company</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>bf31a602</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>00:48</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>Fix check-in/out time shown in UTC + remaining day-row dupe sources</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>d4a76d0e</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>00:47</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>Fix policy-gate redirect loop: exclude real app-prefixed paths</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>c1ffab63</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>00:25</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>Fix policy create 500 + shift-schedule duplicate 500 + day-row dupes</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>3d83adac</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>23:56</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>Add company-side mandatory policy acceptance gate</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>c9717a59</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>23:36</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>Fix work-timer freeze: use local time in at-work calc to match stored clock_in</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>d24bb137</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>23:23</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>Home card: gate pending-leave count on approval perm, not view perm</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>9fd79f8e</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>23:09</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>Work timer: anchor only on run-state flip so it ticks while clocked in</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>62e0559f</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>23:02</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>Fix leaked template comment breaking page JS in in_out_component</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>b86f73fa</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>22:57</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>Fix check-in work timer: one self-healing ticker, not a swapped-in script</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>d2404aa0</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>22:43</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>Allow same-origin framing so /terms/ legal-doc viewer can embed its PDFs</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>ca4bd082</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>21:58</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>Fix attendance employee FK on_delete + harden hx_request_required gate</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>be89105c</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>16:23</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>Consolidate navbar work-timer into one epoch-based ticker</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>3e88283c</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>16:17</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>Add delete-plan button to admin console plan list</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>69a1c82b</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>16:03</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>Subscription plans: yearly pricing, monthly/yearly toggle, plan delete, feature picker</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>c8b75583</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>Register geofencing / live_location / selfie_login as plan feature flags</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>39c490c4</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>15:26</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>Gate home "Tasks &amp; Notifications" admin items behind permissions</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>d9177561</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>15:24</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>Fix attendance history event order (home stuck on "Checked In")</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>1e892335</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>15:11</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>Fix mobile check-in/out state mismatch (single source of truth)</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>75d1457d</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>Fix mobile API: pin tenant context on JWT auth + crash guards</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>e472a8e5</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>Add mobile shift-request endpoints (fixes Flutter 404 on Shift Requests)</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>465ca8c0</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>07:36</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>Flutter merge round 2: payslip xhtml2pdf fallback + companyLeaves dates</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>bf2c35b6</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>07:16</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>Merge Flutter backend compatibility fixes from friend's 13.0.0.beta fork</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>eef59077</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>23:38</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>Honor empty scoped querysets in list views (fix cross-employee data leak)</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>42bcff98</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>22:55</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>Hardcode timer data-run per clock state (default filter treats 0 as falsy)</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>56d8dd18</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>22:53</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>Fix timer reversal/tab-hijack, payslip leak, notifications list, announcement scope</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>05c4f78b</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>22:15</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>Fix frozen work timer: keep forecast in scope for timer script</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>36a9a3bd</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>21:18</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>Scope settings-cache keys per company (fix cross-tenant leaks)</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>52489ab1</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>21:11</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>Restore self-approval block for leave, scoped to CEO/owner tier</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>7225930b</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>21:10</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>Hide higher-tier people's requests from lower tiers</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>b66884fb</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>20:45</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>Set company on announcement create so it is visible</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>8a360d3c</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>17:44</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>Hide higher-tier people from lower tiers in employee directory</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>dc846708</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>21:11</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t>Fix duplicate login and first password form</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>ada107cc</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>21:06</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>Reset company session on login</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>9c4d4416</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>21:03</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="inlineStr">
+        <is>
+          <t>Guard missing payroll settings</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>7effec30</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>Skip old password for first login</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>8da726be</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>20:50</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="inlineStr">
+        <is>
+          <t>Use standalone first password page</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>6ca74a76</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>20:47</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="inlineStr">
+        <is>
+          <t>Fix first-login password change redirect</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>532b3fb4</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>20:42</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="inlineStr">
+        <is>
+          <t>Try all matching login identifiers</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>ddc920fa</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>20:40</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr">
+        <is>
+          <t>Expose login auth diagnostics</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>97f09dc0</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>20:33</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="inlineStr">
+        <is>
+          <t>Add login auth debug logging</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>7b87f0b1</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>20:29</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t>Allow legacy phone password login</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>749c2844</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>20:24</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="inlineStr">
+        <is>
+          <t>Normalize phone-based employee login</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>e1bd6921</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>20:14</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="inlineStr">
+        <is>
+          <t>Use employee phone as initial password</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>2040bdd0</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>19:53</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr">
+        <is>
+          <t>Serialize payslip pay head data safely</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>e1944236</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>19:51</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="inlineStr">
+        <is>
+          <t>Fix employer contribution amount math</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>10c5cb52</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>19:50</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E129" s="2" t="inlineStr">
+        <is>
+          <t>Fix employer contribution rate comparison</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>4ae8b169</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>19:48</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="inlineStr">
+        <is>
+          <t>Fix payslip json serialization</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>a9e9f7e1</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>19:46</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E131" s="2" t="inlineStr">
+        <is>
+          <t>Fix payroll leave deduction decimal math</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>6033a836</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>19:45</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="inlineStr">
+        <is>
+          <t>Preserve employee basic salary percentage</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>ec3d4261</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>19:37</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E133" s="2" t="inlineStr">
+        <is>
+          <t>Allow tenant owners to approve own leave</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>1d27ddfd</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>19:32</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E134" s="2" t="inlineStr">
+        <is>
+          <t>Fix shift schedule company scoping</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>bcdd6c08</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>19:25</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E135" s="2" t="inlineStr">
+        <is>
+          <t>Keep shift day lookup global</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>02f6d728</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>19:22</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="inlineStr">
+        <is>
+          <t>Fix company-scoped day queryset</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>72925556</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>16:29</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E137" s="2" t="inlineStr">
+        <is>
+          <t>Fix task date validation on create</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>64bb9577</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>16:26</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E138" s="2" t="inlineStr">
+        <is>
+          <t>Fix company actions and task form errors</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>bff1d2f5</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>16:18</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E139" s="2" t="inlineStr">
+        <is>
+          <t>Fix company edit action visibility</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>4802c233</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>16:14</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E140" s="2" t="inlineStr">
+        <is>
+          <t>Fix project list request setup</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>715825e2</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>16:12</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E141" s="2" t="inlineStr">
+        <is>
+          <t>Fix company-scoped dropdown leakage</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>3d4f3eda</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E142" s="2" t="inlineStr">
+        <is>
+          <t>fixing leakages</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>835f2c08</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>15:08</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E143" s="2" t="inlineStr">
+        <is>
+          <t>Fix scoped org settings, company edit visibility, modal a11y, and backfill migration</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>ca6e15fb</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E144" s="2" t="inlineStr">
+        <is>
+          <t>Fix 500 errors in clock-out, JSON decode in email automation, and DoesNotExist in job position creation</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>204224d3</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E145" s="2" t="inlineStr">
+        <is>
+          <t>Fix 500 errors in company views and clock-out when work info is missing</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>74c90093</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E146" s="2" t="inlineStr">
+        <is>
+          <t>Fix attendance timer not starting after HTMX swap for both skylinx_theme and generic theme</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>576176cf</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E147" s="2" t="inlineStr">
+        <is>
+          <t>Fix missing edit button for company owners by allowing superusers in _company_is_user_company check</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>1ceaad5f</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>13:16</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E148" s="2" t="inlineStr">
+        <is>
+          <t>Fix 500 error on company list and navbar views due to request.user access in __init__</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>ff2c32af</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E149" s="2" t="inlineStr">
+        <is>
+          <t>Fix duplicate key violation on BonusPoint creation during Employee onboarding</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>1bf75e82</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>12:56</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E150" s="2" t="inlineStr">
+        <is>
+          <t>Fix company list not showing new companies: use is_platform_owner(self.request.user) instead of bare request</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>186d1c43</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>12:44</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E151" s="2" t="inlineStr">
+        <is>
+          <t>Fix dahua.py: use typing.List[int] instead of list[int] for Python 3.8 compat</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>a9b7f018</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>12:41</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E152" s="2" t="inlineStr">
+        <is>
+          <t>Fix Python 3.8 compat in dahua.py, fix JS ReferenceErrors in hour_account.js and index.js</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>055d7473</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E153" s="2" t="inlineStr">
+        <is>
+          <t>Fix 500 error on attendance validation approval and worked hour field initialization</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>dd31d374</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E154" s="2" t="inlineStr">
+        <is>
+          <t>Fix timezone import, tickCheckboxes JS error, and timer update issue</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>93330231</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>12:01</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E155" s="2" t="inlineStr">
+        <is>
+          <t>Fix: Clock-in 500 error due to missing EmployeeShiftDay; Add Create button for employee attendance request</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>ee493a78</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E156" s="2" t="inlineStr">
+        <is>
+          <t>Fix: Add Create button for Attendance Request</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>b41414ad</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>11:39</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E157" s="2" t="inlineStr">
+        <is>
+          <t>Fix: Sidebar visibility for employees</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>d8e24f83</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E158" s="2" t="inlineStr">
+        <is>
+          <t>Fix: Generate missing migrations for multi-tenant upgrade</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>77f141b4</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>11:09</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E159" s="2" t="inlineStr">
+        <is>
+          <t>fix: remove recursive is_platform_owner in context_processors</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>b6485c23</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>10:46</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E160" s="2" t="inlineStr">
+        <is>
+          <t>Security fixes and RBAC implementations for 1.1.0.beta</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>2dbd1465</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E161" s="2" t="inlineStr">
+        <is>
+          <t>Restrict payroll insights and fix shift approval permission</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>d0773b90</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>09:49</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E162" s="2" t="inlineStr">
+        <is>
+          <t>fix: replace vulnerable view_* permission gates with change_ permissions across all apps</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>e9021021</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>04:26</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E163" s="2" t="inlineStr">
+        <is>
+          <t>fix: restrict sidebar/views to self-service for regular employees</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>9ac20a45</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>03:36</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E164" s="2" t="inlineStr">
+        <is>
+          <t>fix: remove extraneous ');' causing syntax error in htmxSelect2 theme file</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>15d36cb6</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>03:06</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E165" s="2" t="inlineStr">
+        <is>
+          <t>fix: use change_employee perm instead of view_employee for dropdown scoping</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>1518bd35</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>02:25</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E166" s="2" t="inlineStr">
+        <is>
+          <t>fix: scope employee dropdown to subordinates for non-admin users; add try-catch to htmxSelect2 HTMX handlers</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>b6529dde</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>01:57</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E167" s="2" t="inlineStr">
+        <is>
+          <t>Fix employee dropdown only showing self, top bar disappearing, select2 errors</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>44227315</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>01:47</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E168" s="2" t="inlineStr">
+        <is>
+          <t>fix: include_employee_instance respects existing queryset, fix htmx:afterSettle select2 init</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>d7c310f2</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>01:41</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E169" s="2" t="inlineStr">
+        <is>
+          <t>fix: employee dropdown only show own employee, fix select2 destroy error</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>9dc4add1</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>01:32</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E170" s="2" t="inlineStr">
+        <is>
+          <t>fix: ensure _saved_filters is always initialized</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>629469d2</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>01:25</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E171" s="2" t="inlineStr">
+        <is>
+          <t>Fix payslip list filter setup</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>97d25386</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>01:05</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E172" s="2" t="inlineStr">
+        <is>
+          <t>Harden payslip visibility and HTMX redirects</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>a603d6a5</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>23:35</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E173" s="2" t="inlineStr">
+        <is>
+          <t>Restrict company switching to platform owner</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>519a678c</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>23:27</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E174" s="2" t="inlineStr">
+        <is>
+          <t>Scope employee choices and guard shell swaps</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>2da73c36</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>23:19</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E175" s="2" t="inlineStr">
+        <is>
+          <t>Add legacy auth table compatibility views</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>b5397b5b</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>23:08</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E176" s="2" t="inlineStr">
+        <is>
+          <t>Fix shared form and notification polling</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>26899b7d</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>22:37</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E177" s="2" t="inlineStr">
+        <is>
+          <t>Pin bank form label targets</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>547b9292</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>21:49</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E178" s="2" t="inlineStr">
+        <is>
+          <t>Disable bank form autocomplete</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>604f5b26</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>21:39</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E179" s="2" t="inlineStr">
+        <is>
+          <t>Fix JS selector in all bank detail templates to find inputs by name to support dynamic form prefixes</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>f5071589</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>21:38</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E180" s="2" t="inlineStr">
+        <is>
+          <t>Apply robust JS fetch logic to bank_details.html</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>0b143d36</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>21:33</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E181" s="2" t="inlineStr">
+        <is>
+          <t>Remove unnecessary conditional check for IFSC fetch that blocked execution</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>a3457440</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>21:23</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E182" s="2" t="inlineStr">
+        <is>
+          <t>Fix IFSC bank details autofill JavaScript</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>59b79ab8</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>21:14</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E183" s="2" t="inlineStr">
+        <is>
+          <t>Fix bugs: enforce company scoping and superuser exclusion for employee querysets across forms and API views</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>3bae1203</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>21:01</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E184" s="2" t="inlineStr">
+        <is>
+          <t>Fix owner account visibility issue in employee dropdowns and update logos</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>e231f2c0</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>20:47</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E185" s="2" t="inlineStr">
+        <is>
+          <t>Fix UI freeze on designation create by using native click</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>023e641e</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>20:23</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E186" s="2" t="inlineStr">
+        <is>
+          <t>Scope document request employees</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>78dee615</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>20:17</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E187" s="2" t="inlineStr">
+        <is>
+          <t>Remove invalid label wrappers</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>9cc49dc8</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>20:13</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E188" s="2" t="inlineStr">
+        <is>
+          <t>Fix bank autofill and label targets</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>26974fd4</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>20:07</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E189" s="2" t="inlineStr">
+        <is>
+          <t>Harden bank IFSC autofill mapping</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>d19f20b3</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E190" s="2" t="inlineStr">
+        <is>
+          <t>Fix IFSC bank autofill</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>275e3c26</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>19:48</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E191" s="2" t="inlineStr">
+        <is>
+          <t>Scope client-facing employee selectors</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>51807365</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>19:36</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E192" s="2" t="inlineStr">
+        <is>
+          <t>Scope user groups to tenant company</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>62497a74</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>19:03</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E193" s="2" t="inlineStr">
+        <is>
+          <t>Scope employee pickers by company</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>048f6ca0</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>18:48</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E194" s="2" t="inlineStr">
+        <is>
+          <t>Restore client company edit action</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>ce80f0aa</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>18:43</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E195" s="2" t="inlineStr">
+        <is>
+          <t>Tighten client company ownership</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>a563612c</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>18:37</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E196" s="2" t="inlineStr">
+        <is>
+          <t>Harden client company scoping</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>b80e9edd</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>17:53</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E197" s="2" t="inlineStr">
+        <is>
+          <t>Scope employee directory to client company</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>cad57a73</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E198" s="2" t="inlineStr">
+        <is>
+          <t>Revert breadcrumb logo to text</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>592341fa</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E199" s="2" t="inlineStr">
+        <is>
+          <t>Simplify dark header logo treatment</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>531ac630</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>12:51</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E200" s="2" t="inlineStr">
+        <is>
+          <t>Tighten header logo spacing</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>e1710a56</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>12:46</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E201" s="2" t="inlineStr">
+        <is>
+          <t>Use updated static logo in breadcrumb</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>5b3da73f</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E202" s="2" t="inlineStr">
+        <is>
+          <t>Use brand logo in theme breadcrumbs</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>91499376</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>12:17</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E203" s="2" t="inlineStr">
+        <is>
+          <t>Fit brand logo into breadcrumbs</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>4c3067fa</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>12:01</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E204" s="2" t="inlineStr">
+        <is>
+          <t>Remove legacy licensing module</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>4b81d7d9</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>00:33</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E205" s="2" t="inlineStr">
+        <is>
+          <t>Optimize database queries: resolve N+1 queries in Employee, Attendance, Recruitment, Leave, Onboarding, and Offboarding modules</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>89831474</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>00:19</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E206" s="2" t="inlineStr">
+        <is>
+          <t>Update verify_performance.py to print query tracebacks</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>5ebbf54c</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>00:14</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E207" s="2" t="inlineStr">
+        <is>
+          <t>Update verify_performance.py to print top duplicated queries</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>994c8b77</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>00:09</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E208" s="2" t="inlineStr">
+        <is>
+          <t>Phase 2 global N+1 query performance optimizations for Leave, Onboarding, Offboarding, Recruitment, Payroll, and Employee modules</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>b0f16c4f</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>23:51</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E209" s="2" t="inlineStr">
+        <is>
+          <t>Restore DEBUG = False at the end of verify_performance.py execution</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>8b764bde</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>23:49</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E210" s="2" t="inlineStr">
+        <is>
+          <t>Enable debug mode in verification script to force query logging on production settings</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>698ef773</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>23:46</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E211" s="2" t="inlineStr">
+        <is>
+          <t>Fix contract_list template syntax errors, mock request._messages in verification script, and finalize prefetch related queries</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>2ec5b60b</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>23:42</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E212" s="2" t="inlineStr">
+        <is>
+          <t>Override ALLOWED_HOSTS in verify_performance.py to allow running in prod</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>67b27c9c</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>23:40</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E213" s="2" t="inlineStr">
+        <is>
+          <t>Add performance verification script</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>d2650813</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>23:28</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E214" s="2" t="inlineStr">
+        <is>
+          <t>Optimize EmployeeFilter permission query and edit_accessibility filter to resolve N+1 queries</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>7a88fc62</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>23:12</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E215" s="2" t="inlineStr">
+        <is>
+          <t>Optimize query performance globally with select_related and prefetch_related</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>0183148b</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E216" s="2" t="inlineStr">
+        <is>
+          <t>Fix N+1 query issue in attendance_view and attendance_search</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>09b434fe</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>22:57</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E217" s="2" t="inlineStr">
+        <is>
+          <t>Fix Department attribute access in performance diagnostic script</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>753b4c73</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>22:55</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E218" s="2" t="inlineStr">
+        <is>
+          <t>Add database performance diagnostic script</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>73ad09f1</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>22:31</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E219" s="2" t="inlineStr">
+        <is>
+          <t>Fix remaining missing jQuery [0].click() patterns across other modules</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>6b408353</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>22:25</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E220" s="2" t="inlineStr">
+        <is>
+          <t>Fix UI rendering freeze due to empty selector clicks and decouple HTMX tabs</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>47af16c1</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>20:11</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E221" s="2" t="inlineStr">
+        <is>
+          <t>chore(branding): refresh EMPLINX logo assets (new artwork)</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>80d747ce</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>20:01</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E222" s="2" t="inlineStr">
+        <is>
+          <t>feat(landing-page): redirect login and get started buttons directly to app.emplinx.com</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>d07ee0f2</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>19:18</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E223" s="2" t="inlineStr">
+        <is>
+          <t>feat(employee-ui): suppress Configuration bottom-menu when no sub-items are accessible to the user</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>db416a58</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>19:18</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E224" s="2" t="inlineStr">
+        <is>
+          <t>feat(employee-ui): gate restricted leaves bulk selection checkboxes on delete_restrictleave permission</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>f40a3359</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>19:18</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E225" s="2" t="inlineStr">
+        <is>
+          <t>feat(employee-ui): gate attendance requests Actions dropdown on change_attendance permission</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>7dd2a73d</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>17:44</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E226" s="2" t="inlineStr">
+        <is>
+          <t>chore(static): drop duplicate skylinx-logo.png to silence collectstatic warning</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>f37a83a3</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>17:44</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E227" s="2" t="inlineStr">
+        <is>
+          <t>fix(ui): broken sidebar company logo + remove leaked multi-line comments</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>670d2955</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>17:34</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E228" s="2" t="inlineStr">
+        <is>
+          <t>feat(employee-ui): drop duplicate Restrict Leaves from Configuration menu</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>6004678b</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E229" s="2" t="inlineStr">
+        <is>
+          <t>fix(branding): update the other skylinx-logo.png copies (collectstatic dedupe)</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>293986ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>17:19</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E230" s="2" t="inlineStr">
+        <is>
+          <t>feat(employee-ui): strip approve/reject/bulk/delete actions for employees</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>1d8da431</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>17:16</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E231" s="2" t="inlineStr">
+        <is>
+          <t>feat(employee-ui): hide admin attendance/leave-approval pages from employees</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>50af2af2</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>17:13</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E232" s="2" t="inlineStr">
+        <is>
+          <t>chore(branding+leave): new EMPLINX logo in all 3 slots; drop debug logging</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>1c38dbb2</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>17:04</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E233" s="2" t="inlineStr">
+        <is>
+          <t>fix(leave): tenant leave-type rejected as invalid choice on apply</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>7b16a884</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>16:59</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E234" s="2" t="inlineStr">
+        <is>
+          <t>fix(leave): surface silent failures in per-leave-type apply (MyLeaveRequestSingleForm)</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>f2c88147</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>16:51</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E235" s="2" t="inlineStr">
+        <is>
+          <t>fix(leave): force own-employee on create + log create path</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>3d925753</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>16:37</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E236" s="2" t="inlineStr">
+        <is>
+          <t>fix(js): no_perm.html Alpine crash bricked htmx on the whole page</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>fe365345</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E237" s="2" t="inlineStr">
+        <is>
+          <t>fix(leave): remove interview-conflict hijack from objectCreateModal flow too</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>6a9fbd27</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>15:27</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E238" s="2" t="inlineStr">
+        <is>
+          <t>fix(leave): use {% comment %} not multi-line {# #} (leaked text into modal)</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>98915ef5</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>15:17</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E239" s="2" t="inlineStr">
+        <is>
+          <t>fix(leave+rbac): employee leave Save works; HR Manager can manage permissions</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>e3d2f023</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>15:09</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E240" s="2" t="inlineStr">
+        <is>
+          <t>fix(profile): tabs stuck on rendering until refresh</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>9237196b</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>15:01</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E241" s="2" t="inlineStr">
+        <is>
+          <t>fix(leave): reliable Save submit + remove duplicate allocation sidebar entry</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>447abb07</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>13:18</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E242" s="2" t="inlineStr">
+        <is>
+          <t>Fix script tags, conflict check date logic, and AJAX error fallback</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>1fc33074</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>13:07</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E243" s="2" t="inlineStr">
+        <is>
+          <t>Fix leave request validation and available leave count query errors</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>ed8e682e</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>12:41</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E244" s="2" t="inlineStr">
+        <is>
+          <t>fix(leave): resolve leave approval HTML display and employee leave request creation failures</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>5bbac915</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E245" s="2" t="inlineStr">
+        <is>
+          <t>fix: resolved disconnected form submission warning and updated landing page</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>5d610feb</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>11:42</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E246" s="2" t="inlineStr">
+        <is>
+          <t>fix: generate migrations for reimbursement type choices and fix windows console encoding warning</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>a2e52f9c</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>11:38</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E247" s="2" t="inlineStr">
+        <is>
+          <t>fix(payroll): remove contract field from UI, rename remaining reimbursement occurrences to expenses</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>18a0a54c</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E248" s="2" t="inlineStr">
+        <is>
+          <t>fix(auth): make terms check robust with autofill and rename company from Skylinx to EMPLINX</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>e9d1824f</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E249" s="2" t="inlineStr">
+        <is>
+          <t>feat: Add dynamic T&amp;C validation on login and rename software to EMPLINX</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>b0cd8a99</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>10:41</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E250" s="2" t="inlineStr">
+        <is>
+          <t>chore: rename Reimbursement/Encashment to Expenses on UI</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>38a447fb</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E251" s="2" t="inlineStr">
+        <is>
+          <t>fix(payroll): remove contract column from payregister table and change visible contract text to register</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>572c17e0</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>10:13</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E252" s="2" t="inlineStr">
+        <is>
+          <t>fix(cbv): resolve AttributeError by dynamically looking up view class path when dynamic_create_path is missing</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>1feef595</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E253" s="2" t="inlineStr">
+        <is>
+          <t>fix: correct document request permission typos</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>05973a3e</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>09:29</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E254" s="2" t="inlineStr">
+        <is>
+          <t>Fix company badge on the themed User Group list</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>053da5f0</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>09:07</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E255" s="2" t="inlineStr">
+        <is>
+          <t>Legal docs: owner uploads PDFs, public /terms/ shows an inline viewer</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>4e2fb493</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>08:59</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E256" s="2" t="inlineStr">
+        <is>
+          <t>Login: required T&amp;C acceptance checkbox + owner-editable terms link</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>30f679ad</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>08:35</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E257" s="2" t="inlineStr">
+        <is>
+          <t>Port Flutter mobile API (/api/v1) from 13.0.0.beta</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>aa3c4807</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>08:24</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E258" s="2" t="inlineStr">
+        <is>
+          <t>Owner: tag each user group with its company in the group list</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>47b56e3f</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>08:13</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E259" s="2" t="inlineStr">
+        <is>
+          <t>Fix: Lock PMS menu in templates/sidebar.html to prevent permission errors</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>aa3bfafc</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>01:45</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E260" s="2" t="inlineStr">
+        <is>
+          <t>Fix dynamic-path 404 caching issue, fix HTMX 400 error, rename Reimbursement/Encashment to Expenses, rename contract to register</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>a393f1cd</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>01:12</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E261" s="2" t="inlineStr">
+        <is>
+          <t>Fix document request permissions for regular employees and move pms to bottom of sidebar</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>b7531139</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>00:42</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E262" s="2" t="inlineStr">
+        <is>
+          <t>Remove passport references from seed data</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>66f8c4b9</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>00:38</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E263" s="2" t="inlineStr">
+        <is>
+          <t>Self-healing company role perms + Company Admin backfill</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>f725c447</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>00:32</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E264" s="2" t="inlineStr">
+        <is>
+          <t>Grant document (skylinx_documents) perms to company admin / HR Manager</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>a0d6a9d2</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>00:29</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E265" s="2" t="inlineStr">
+        <is>
+          <t>Update HRMS: Renamed contracts to registers, reimbursements to expenses, handle dynamic request errors, and hide 0 OT attendances tab</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>271f624e</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>23:53</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E266" s="2" t="inlineStr">
+        <is>
+          <t>Salary: single Basic % drives monthly basic in pay register</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>49427492</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>23:43</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E267" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard cards: force hard navigation (keep app chrome)</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>7f2413e5</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>23:29</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E268" s="2" t="inlineStr">
+        <is>
+          <t>Fix dashboard 500: register missing dashboard API URLs</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>cd02b78e</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>23:20</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E269" s="2" t="inlineStr">
+        <is>
+          <t>Guide: use server IP (domain pending), redact owner password</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>c8308001</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>23:15</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E270" s="2" t="inlineStr">
+        <is>
+          <t>Add GO_LIVE_GUIDE: platform setup, onboarding, roles, HR walkthrough</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>06cdbd13</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E271" s="2" t="inlineStr">
+        <is>
+          <t>Bug fixes + drop redundant setup_client command</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>beadc5bb</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>22:39</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E272" s="2" t="inlineStr">
+        <is>
+          <t>Reconcile migration state for production safety</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>325d4f5d</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>22:32</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E273" s="2" t="inlineStr">
+        <is>
+          <t>Tenant isolation hardening + client provisioning (v1.0.2.beta)</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>d17e2c4c</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>19:27</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E274" s="2" t="inlineStr">
+        <is>
+          <t>Fix migration 0013: use IF EXISTS drops for Postgres compatibility</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>c9632095</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>19:01</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E275" s="2" t="inlineStr">
+        <is>
+          <t>Apply CTC percentage inputs to UpdateForm too (the actual edit panel)</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>e61d1e83</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>18:57</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E276" s="2" t="inlineStr">
+        <is>
+          <t>Salary components editable from UI (Basic/HRA/Other %) instead of raw JSON</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>af2b7ec3</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>18:56</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E277" s="2" t="inlineStr">
+        <is>
+          <t>fix: import django_apps globally in base/views.py to resolve NameError in group_permissions_table_view</t>
+        </is>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>e3d9ec57</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>18:53</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E278" s="2" t="inlineStr">
+        <is>
+          <t>Replace probation_end date with probation_days; CTC with dynamic salary components</t>
+        </is>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>ba739776</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>18:43</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E279" s="2" t="inlineStr">
+        <is>
+          <t>feat: make holiday calendar weekend highlighting dynamic based on company leaves</t>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>6834c7ad</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>18:36</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E280" s="2" t="inlineStr">
+        <is>
+          <t>fix(perms): use appconfig verbose_name in all views</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>ccde2f66</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>18:28</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E281" s="2" t="inlineStr">
+        <is>
+          <t>fix(perms): use appconfig verbose_name in user_group view</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>249f079e</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E282" s="2" t="inlineStr">
+        <is>
+          <t>Tasks #4 #8 #10: Aadhar card, hidden permissions, My Payslips</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>4dbc558d</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E283" s="2" t="inlineStr">
+        <is>
+          <t>Fix permission lazy panel: checked state now uses lowercase app_label</t>
+        </is>
+      </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>b0d0138b</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>17:46</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E284" s="2" t="inlineStr">
+        <is>
+          <t>chore: remove skylinx prefix from permission names</t>
+        </is>
+      </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>f654a389</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>17:18</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E285" s="2" t="inlineStr">
+        <is>
+          <t>Company admins page: prevent an admin from revoking their own access</t>
+        </is>
+      </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>28cf8ddd</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>17:09</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E286" s="2" t="inlineStr">
+        <is>
+          <t>Fix document approve/reject buttons hidden by app-label typo</t>
+        </is>
+      </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>70461960</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>17:07</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E287" s="2" t="inlineStr">
+        <is>
+          <t>Prohibition rules: block flagged leave during probation + email HR on probation end</t>
+        </is>
+      </c>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>f0ef90d6</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>17:03</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E288" s="2" t="inlineStr">
+        <is>
+          <t>Add probation end date to employee work info + profile</t>
+        </is>
+      </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>90bece3c</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>16:59</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E289" s="2" t="inlineStr">
+        <is>
+          <t>Auto-assign company to employee work info on save</t>
+        </is>
+      </c>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>084bb611</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>16:47</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E290" s="2" t="inlineStr">
+        <is>
+          <t>Expenses page: single unified claims section with 7 categories</t>
+        </is>
+      </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>d5b29d90</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>16:42</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E291" s="2" t="inlineStr">
+        <is>
+          <t>Attendance/menu cleanup: remove OT tab, work records, work-type requests; relocate Holidays to Calendar</t>
+        </is>
+      </c>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>35b10abd</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>16:14</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E292" s="2" t="inlineStr">
+        <is>
+          <t>Fix permission toggle: lazy panel also used title-cased app label as value</t>
+        </is>
+      </c>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>e42966de</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>15:51</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E293" s="2" t="inlineStr">
+        <is>
+          <t>Replace gorilla 404 image with clean inline SVG</t>
+        </is>
+      </c>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t>fba92ab0</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E294" s="2" t="inlineStr">
+        <is>
+          <t>Fix group permission assignment + deploy settings for http/IP boxes</t>
+        </is>
+      </c>
+      <c r="F294" t="inlineStr">
+        <is>
+          <t>7e34ee1e</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>12:41</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E295" s="2" t="inlineStr">
+        <is>
+          <t>Remove emojis from holiday calendar</t>
+        </is>
+      </c>
+      <c r="F295" t="inlineStr">
+        <is>
+          <t>b8f2e00e</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E296" s="2" t="inlineStr">
+        <is>
+          <t>Leave: optional holidays count as working days; only mandatory excluded</t>
+        </is>
+      </c>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t>ef863af9</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E297" s="2" t="inlineStr">
+        <is>
+          <t>Holiday optional/mandatory: model flag, form toggle, calendar colors</t>
+        </is>
+      </c>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t>d9203ee7</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>12:24</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E298" s="2" t="inlineStr">
+        <is>
+          <t>Currency: default $ -&gt; rupee, prefix (context processor + migrate existing)</t>
+        </is>
+      </c>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>601ab369</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>12:16</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E299" s="2" t="inlineStr">
+        <is>
+          <t>Remove Hourly wage type option (not used)</t>
+        </is>
+      </c>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t>cd299c73</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>11:56</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E300" s="2" t="inlineStr">
+        <is>
+          <t>Hide Timesheet, drop Work Type &amp; Shift profile tab, rename Work From Office -&gt; Onsite</t>
+        </is>
+      </c>
+      <c r="F300" t="inlineStr">
+        <is>
+          <t>41d98e03</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>11:24</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E301" s="2" t="inlineStr">
+        <is>
+          <t>fix: register holiday-calendar-view URL in base/urls.py (was causing NoReverseMatch)</t>
+        </is>
+      </c>
+      <c r="F301" t="inlineStr">
+        <is>
+          <t>5984a82a</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E302" s="2" t="inlineStr">
+        <is>
+          <t>feat: safely ported Sandeep's features (dashboard, sidebar, attendance cleanup, holiday calendar, button labels)</t>
+        </is>
+      </c>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t>db05a78a</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>10:27</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E303" s="2" t="inlineStr">
+        <is>
+          <t>fix: resolve TemplateSyntaxError due to trailing endif tag</t>
+        </is>
+      </c>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>5bc1a381</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>10:13</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E304" s="2" t="inlineStr">
+        <is>
+          <t>UI updates: Hide work type for self, rename badge id to employee id, restrict subscription visibility</t>
+        </is>
+      </c>
+      <c r="F304" t="inlineStr">
+        <is>
+          <t>d7feefc8</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>09:08</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E305" s="2" t="inlineStr">
+        <is>
+          <t>Hide remaining Bonus Points UI: PMS dashboard pts + Add Bonus button</t>
+        </is>
+      </c>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t>0dc8b586</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>09:01</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E306" s="2" t="inlineStr">
+        <is>
+          <t>Actually hide extra profile tabs: KEEP_TABS was on the wrong subclass</t>
+        </is>
+      </c>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>6ab62eb3</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>08:54</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E307" s="2" t="inlineStr">
+        <is>
+          <t>Fix two real bugs from audit: inline-thread + EmployeeTask save</t>
+        </is>
+      </c>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t>09f634da</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>08:41</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E308" s="2" t="inlineStr">
+        <is>
+          <t>Fix prod 400: manifest storage rejected leading-slash {% static %} paths</t>
+        </is>
+      </c>
+      <c r="F308" t="inlineStr">
+        <is>
+          <t>bd50dd72</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>07:46</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E309" s="2" t="inlineStr">
+        <is>
+          <t>Fix real bugs from audit: clean(), encashment typo, __str__ DB write, ContentType, CONN_MAX_AGE</t>
+        </is>
+      </c>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t>15961bd0</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>07:19</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E310" s="2" t="inlineStr">
+        <is>
+          <t>Fix static perf: Django 6 ignores STATICFILES_STORAGE, use STORAGES</t>
+        </is>
+      </c>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t>d3c25015</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>07:14</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E311" s="2" t="inlineStr">
+        <is>
+          <t>Static: manifest storage for 1yr immutable caching (was max-age=60)</t>
+        </is>
+      </c>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>2e80123e</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>07:02</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E312" s="2" t="inlineStr">
+        <is>
+          <t>Perf: skip dead DB-template loader + fix sidebar cache invalidation</t>
+        </is>
+      </c>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>c6e88a23</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E313" s="2" t="inlineStr">
+        <is>
+          <t>Perf: auto select_related on all list views + memoize site/company per request</t>
+        </is>
+      </c>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t>57e0ff99</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>06:39</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E314" s="2" t="inlineStr">
+        <is>
+          <t>Speed up employee list/card: select_related kills N+1 on work info</t>
+        </is>
+      </c>
+      <c r="F314" t="inlineStr">
+        <is>
+          <t>4325558c</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>22:22</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E315" s="2" t="inlineStr">
+        <is>
+          <t>Page inventory: number all entries 1..2926 + tag hidden features</t>
+        </is>
+      </c>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t>b3e2e6fe</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>22:13</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E316" s="2" t="inlineStr">
+        <is>
+          <t>Page inventory: add tab-views (add_tab) + complete unfiltered route dump</t>
+        </is>
+      </c>
+      <c r="F316" t="inlineStr">
+        <is>
+          <t>644de12d</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>21:58</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E317" s="2" t="inlineStr">
+        <is>
+          <t>Add full page inventory (menu + all page-views, partials, review list)</t>
+        </is>
+      </c>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>cbe50913</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>21:53</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E318" s="2" t="inlineStr">
+        <is>
+          <t>Hide Timesheet from Projects menu</t>
+        </is>
+      </c>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>47af578f</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>21:33</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E319" s="2" t="inlineStr">
+        <is>
+          <t>Remove My Profile from Employee menu (reachable via top-right profile)</t>
+        </is>
+      </c>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>581d0646</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>21:32</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E320" s="2" t="inlineStr">
+        <is>
+          <t>Profile cleanup: declutter tabs, blood group, hide bonus/roster</t>
+        </is>
+      </c>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t>6ba0b33a</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>17:32</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E321" s="2" t="inlineStr">
+        <is>
+          <t>Sandeep modifications: company-admin branding, social links, announcements, shift roster hidden</t>
+        </is>
+      </c>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t>f03f1d08</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E322" s="2" t="inlineStr">
+        <is>
+          <t>OTP password reset + welcome emails + host-aware links (no hardcoded domain)</t>
+        </is>
+      </c>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>3d04ee3c</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>16:23</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E323" s="2" t="inlineStr">
+        <is>
+          <t>Owner Analytics &amp; Access hub (/manage/analytics)</t>
+        </is>
+      </c>
+      <c r="F323" t="inlineStr">
+        <is>
+          <t>8b55a907</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>16:09</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E324" s="2" t="inlineStr">
+        <is>
+          <t>Antigravity: RBAC permission fixes + plan CRUD templates + seat_override migration</t>
+        </is>
+      </c>
+      <c r="F324" t="inlineStr">
+        <is>
+          <t>74252520</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>15:59</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E325" s="2" t="inlineStr">
+        <is>
+          <t>Clarify module/feature state in owner console</t>
+        </is>
+      </c>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t>386a7b69</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>15:52</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E326" s="2" t="inlineStr">
+        <is>
+          <t>Cap bulk employee import at the plan's seat limit</t>
+        </is>
+      </c>
+      <c r="F326" t="inlineStr">
+        <is>
+          <t>ad65b90c</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E327" s="2" t="inlineStr">
+        <is>
+          <t>Client ID + support contact for clients (matches owner console)</t>
+        </is>
+      </c>
+      <c r="F327" t="inlineStr">
+        <is>
+          <t>6984259d</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E328" s="2" t="inlineStr">
+        <is>
+          <t>Sidebar reflects plan + schedule subscription expiry sweep</t>
+        </is>
+      </c>
+      <c r="F328" t="inlineStr">
+        <is>
+          <t>256952f8</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>15:41</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E329" s="2" t="inlineStr">
+        <is>
+          <t>Enforce employee seat limit + seat-usage warning banner</t>
+        </is>
+      </c>
+      <c r="F329" t="inlineStr">
+        <is>
+          <t>93e0980a</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E330" s="2" t="inlineStr">
+        <is>
+          <t>Show Projects/Helpdesk for company admins (missing app perms)</t>
+        </is>
+      </c>
+      <c r="F330" t="inlineStr">
+        <is>
+          <t>deb0d254</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>13:07</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E331" s="2" t="inlineStr">
+        <is>
+          <t>Fix employee-permission views gated on add_permission (company admins blocked)</t>
+        </is>
+      </c>
+      <c r="F331" t="inlineStr">
+        <is>
+          <t>474b65a9</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>12:58</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E332" s="2" t="inlineStr">
+        <is>
+          <t>Fix group permissions save: gate on change_group, not add_permission</t>
+        </is>
+      </c>
+      <c r="F332" t="inlineStr">
+        <is>
+          <t>b57ade38</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>12:52</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E333" s="2" t="inlineStr">
+        <is>
+          <t>Fix group permissions not saving + select-all in lazy panel</t>
+        </is>
+      </c>
+      <c r="F333" t="inlineStr">
+        <is>
+          <t>0729cea0</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>12:43</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E334" s="2" t="inlineStr">
+        <is>
+          <t>Vendor console: set client admin password + show login username; fix Roles select-all</t>
+        </is>
+      </c>
+      <c r="F334" t="inlineStr">
+        <is>
+          <t>28acd49e</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>12:33</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E335" s="2" t="inlineStr">
+        <is>
+          <t>Seed default per-company roles (HR Manager / Manager / Employee)</t>
+        </is>
+      </c>
+      <c r="F335" t="inlineStr">
+        <is>
+          <t>c48a9c4b</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>12:23</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E336" s="2" t="inlineStr">
+        <is>
+          <t>Fix login() backend error on impersonate/signup/onboarding</t>
+        </is>
+      </c>
+      <c r="F336" t="inlineStr">
+        <is>
+          <t>7942d84d</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E337" s="2" t="inlineStr">
+        <is>
+          <t>Fix password reset (Site.DoesNotExist) + stop login autofill</t>
+        </is>
+      </c>
+      <c r="F337" t="inlineStr">
+        <is>
+          <t>7b5b054c</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>11:54</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E338" s="2" t="inlineStr">
+        <is>
+          <t>Password reset: send to all of the employee's addresses</t>
+        </is>
+      </c>
+      <c r="F338" t="inlineStr">
+        <is>
+          <t>9748d357</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>11:44</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E339" s="2" t="inlineStr">
+        <is>
+          <t>Fix employee login (email OR phone) + password reset email delivery</t>
+        </is>
+      </c>
+      <c r="F339" t="inlineStr">
+        <is>
+          <t>a2473a4f</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>11:23</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E340" s="2" t="inlineStr">
+        <is>
+          <t>Fix multi-tenant employee leak: lock non-superusers to own company</t>
+        </is>
+      </c>
+      <c r="F340" t="inlineStr">
+        <is>
+          <t>b5891d50</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E341" s="2" t="inlineStr">
+        <is>
+          <t>Wire feature_overrides into middleware gate + console cleanup</t>
+        </is>
+      </c>
+      <c r="F341" t="inlineStr">
+        <is>
+          <t>4788c80e</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E342" s="2" t="inlineStr">
+        <is>
+          <t>Vendor console feature toggles + fix company admin group perms</t>
+        </is>
+      </c>
+      <c r="F342" t="inlineStr">
+        <is>
+          <t>717028b8</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>10:43</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E343" s="2" t="inlineStr">
+        <is>
+          <t>#6 Friendly roles page + #10 Skylinx logo always in sidebar</t>
+        </is>
+      </c>
+      <c r="F343" t="inlineStr">
+        <is>
+          <t>53795274</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E344" s="2" t="inlineStr">
+        <is>
+          <t>Survival/critical pass: backups, deploy, webhook, trial warnings, multi-admin, SMTP</t>
+        </is>
+      </c>
+      <c r="F344" t="inlineStr">
+        <is>
+          <t>2fe2a57f</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/worklog.xlsx
+++ b/docs/worklog.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F344"/>
+  <dimension ref="A1:F360"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -11447,6 +11447,518 @@
         </is>
       </c>
     </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>01:24</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E345" s="2" t="inlineStr">
+        <is>
+          <t>Smoke-test round 2: remaining export + notification-sound crashes</t>
+        </is>
+      </c>
+      <c r="F345" t="inlineStr">
+        <is>
+          <t>dfb86e27</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>01:21</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E346" s="2" t="inlineStr">
+        <is>
+          <t>Smoke-test audit: fix 9 crashing endpoints across modules</t>
+        </is>
+      </c>
+      <c r="F346" t="inlineStr">
+        <is>
+          <t>98570f2e</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>00:52</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E347" s="2" t="inlineStr">
+        <is>
+          <t>Fix Python 3.8 import crash in announcement API (list[dict] hint)</t>
+        </is>
+      </c>
+      <c r="F347" t="inlineStr">
+        <is>
+          <t>54d174ac</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>00:45</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E348" s="2" t="inlineStr">
+        <is>
+          <t>Offboarding audit: resignation-delete IDOR, unguarded gets, UTC notice date</t>
+        </is>
+      </c>
+      <c r="F348" t="inlineStr">
+        <is>
+          <t>45964406</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>00:40</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E349" s="2" t="inlineStr">
+        <is>
+          <t>Project audit: fix undefined-date 500, cross-project stage move, employee_get crash</t>
+        </is>
+      </c>
+      <c r="F349" t="inlineStr">
+        <is>
+          <t>dcd04456</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>00:27</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E350" s="2" t="inlineStr">
+        <is>
+          <t>Asset audit: fix list-view crash, asset-count 500, dead duplicate manager</t>
+        </is>
+      </c>
+      <c r="F350" t="inlineStr">
+        <is>
+          <t>3b064d68</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>00:21</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E351" s="2" t="inlineStr">
+        <is>
+          <t>PMS audit: feedback submit IDOR, objective-view crash, feedback close-loop bug</t>
+        </is>
+      </c>
+      <c r="F351" t="inlineStr">
+        <is>
+          <t>82ac3bbf</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>00:13</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E352" s="2" t="inlineStr">
+        <is>
+          <t>Recruitment audit: survey perm gap, 2 crashes, delete-order data loss, UTC</t>
+        </is>
+      </c>
+      <c r="F352" t="inlineStr">
+        <is>
+          <t>e17cfeb5</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>evening</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>Geofencing</t>
+        </is>
+      </c>
+      <c r="E353" s="2" t="inlineStr">
+        <is>
+          <t>Added GeoFencing.enforce BooleanField (default False, opt-in) so out-of-zone check-in/out can be hard-blocked instead of just flagged + admin-notified</t>
+        </is>
+      </c>
+      <c r="F353" t="inlineStr">
+        <is>
+          <t>geofencing/models.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>evening</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>Attendance/Mobile</t>
+        </is>
+      </c>
+      <c r="E354" s="2" t="inlineStr">
+        <is>
+          <t>MobileCheckInAPIView and MobileCheckOutAPIView now return 400 OUTSIDE_GEOFENCE (with distanceFromCenterMeters) when within_geofence is False and geofence.enforce is True</t>
+        </is>
+      </c>
+      <c r="F354" t="inlineStr">
+        <is>
+          <t>skylinx_api/api_views/attendance/mobile_views.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>evening</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>Fix</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>Attendance</t>
+        </is>
+      </c>
+      <c r="E355" s="2" t="inlineStr">
+        <is>
+          <t>Removed stray `from datetime import timezone` in views.py that was shadowing django.utils.timezone and silently breaking .now()/.localtime() calls in this file</t>
+        </is>
+      </c>
+      <c r="F355" t="inlineStr">
+        <is>
+          <t>skylinx_api/api_views/attendance/views.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>evening</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>Fix</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>Attendance</t>
+        </is>
+      </c>
+      <c r="E356" s="2" t="inlineStr">
+        <is>
+          <t>ClockInAPIView day-row lookup (today + yesterday) no longer raises DoesNotExist when EmployeeShiftDay's company M2M is unlinked for the tenant: falls back through company-scoped filter -&gt; entire() -&gt; create(day=...)</t>
+        </is>
+      </c>
+      <c r="F356" t="inlineStr">
+        <is>
+          <t>skylinx_api/api_views/attendance/views.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>23:56</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E357" s="2" t="inlineStr">
+        <is>
+          <t>Employee audit: fix document IDOR, anon dynamic-create, 2 crashes, UTC dates</t>
+        </is>
+      </c>
+      <c r="F357" t="inlineStr">
+        <is>
+          <t>89227295</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>22:58</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E358" s="2" t="inlineStr">
+        <is>
+          <t>Leave audit: fix bulk-delete IDOR + 3 unguarded .get() 500s</t>
+        </is>
+      </c>
+      <c r="F358" t="inlineStr">
+        <is>
+          <t>09c0ed9c</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>22:44</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E359" s="2" t="inlineStr">
+        <is>
+          <t>Payroll audit: fix perm gap, null-wage/rate crashes, UTC month bugs</t>
+        </is>
+      </c>
+      <c r="F359" t="inlineStr">
+        <is>
+          <t>cbf40aa8</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>21:13</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
+      <c r="E360" s="2" t="inlineStr">
+        <is>
+          <t>Audit attendance: fix API crashes, add configurable geofence enforcement</t>
+        </is>
+      </c>
+      <c r="F360" t="inlineStr">
+        <is>
+          <t>a65effb3</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
